--- a/config/cityscene.xlsx
+++ b/config/cityscene.xlsx
@@ -1,12 +1,12 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" windowWidth="27945" windowHeight="12375" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="cityscene" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="cityscene" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
@@ -1144,7 +1144,7 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
-          <t>初期設定シーン</t>
+          <t>初始设置场景</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
@@ -1171,7 +1171,7 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>オズの魔法使い</t>
+          <t>绿野仙踪</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
@@ -1198,7 +1198,7 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>ナイトソングウッド</t>
+          <t>奈特森伍德</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
